--- a/Bases_de_Dados/FootyStats/Europe UEFA Champions League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Europe UEFA Champions League_20252026.xlsx
@@ -23258,7 +23258,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Chelsea (AUS)</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -23368,7 +23368,7 @@
         <v>2.63</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR105" t="n">
         <v>0</v>
@@ -25545,19 +25545,19 @@
         <v>2</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ115" t="n">
         <v>1.36</v>
       </c>
       <c r="AR115" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS115" t="n">
         <v>1.5</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.5</v>
+        <v>2.57</v>
       </c>
       <c r="AU115" t="n">
         <v>3</v>
@@ -31425,13 +31425,13 @@
         <v>3.85</v>
       </c>
       <c r="AN142" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AO142" t="n">
         <v>0</v>
       </c>
       <c r="AP142" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>0.75</v>
@@ -34916,22 +34916,22 @@
         <v>2.33</v>
       </c>
       <c r="AO158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP158" t="n">
         <v>1.56</v>
       </c>
       <c r="AQ158" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR158" t="n">
         <v>1.55</v>
       </c>
       <c r="AS158" t="n">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AT158" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AU158" t="n">
         <v>3</v>
@@ -37529,25 +37529,25 @@
         <v>1.62</v>
       </c>
       <c r="AN170" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AO170" t="n">
         <v>1.75</v>
       </c>
       <c r="AP170" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ170" t="n">
         <v>2</v>
       </c>
       <c r="AR170" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AS170" t="n">
         <v>1.87</v>
       </c>
       <c r="AT170" t="n">
-        <v>3.66</v>
+        <v>3.48</v>
       </c>
       <c r="AU170" t="n">
         <v>6</v>
@@ -41892,22 +41892,22 @@
         <v>2</v>
       </c>
       <c r="AO190" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AP190" t="n">
         <v>1.6</v>
       </c>
       <c r="AQ190" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR190" t="n">
         <v>1.59</v>
       </c>
       <c r="AS190" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="AT190" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="AU190" t="n">
         <v>4</v>
@@ -47775,25 +47775,25 @@
         <v>4.25</v>
       </c>
       <c r="AN217" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO217" t="n">
         <v>1.67</v>
       </c>
       <c r="AP217" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AQ217" t="n">
         <v>1.64</v>
       </c>
       <c r="AR217" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AS217" t="n">
         <v>1.16</v>
       </c>
       <c r="AT217" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="AU217" t="n">
         <v>7</v>
@@ -49522,22 +49522,22 @@
         <v>1.14</v>
       </c>
       <c r="AO225" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AP225" t="n">
         <v>1</v>
       </c>
       <c r="AQ225" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AR225" t="n">
         <v>1.42</v>
       </c>
       <c r="AS225" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AT225" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AU225" t="n">
         <v>5</v>
